--- a/docs/jp/08_反復実績記録.xlsx
+++ b/docs/jp/08_反復実績記録.xlsx
@@ -162,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -208,7 +208,10 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -704,15 +707,9 @@
       <c r="C11" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="C11:E11"/>
+  <mergeCells count="2">
+    <mergeCell ref="B2:E3"/>
     <mergeCell ref="B4:E4"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="B2:E3"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C10:E10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -771,7 +768,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>M-01</t>
@@ -793,29 +790,29 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>M-02</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>AI 平台 4 種展開 整備 開始</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>Claude Projects 先行整備</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>M-03</t>
@@ -837,29 +834,29 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>M-04</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>NotebookLM 構成転換 (3 ノートブック → 1 ノートブック × 42 文献)</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>v1 SUPERSEDED → v2 確定</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>M-05</t>
@@ -881,29 +878,29 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>M-06</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Phase 5 確認関門 開始 (4 平台横断)</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>第 28 番目独立確認担当の作業着手</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
+    <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>M-07</t>
@@ -925,29 +922,29 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>M-08</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>公開発布版 v1.0 確定 (4 平台 LIVE 揃え)</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>公開タグ v1.0-company-release 付与</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
+    <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>M-09</t>
@@ -969,29 +966,29 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>M-10</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>iTMS 様向け納品ドキュメント整備 開始</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>PLAN.md / EXECUTION_PLAN.md 起草 + Phase 0 / 0.5 / 0.7 完了</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
+    <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>M-11</t>
@@ -1013,29 +1010,29 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>M-12</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>Excel 基盤確定 + 用語集骨格確定</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>第 2 回独立確認 無条件合格</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
+    <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>M-13</t>
@@ -1057,29 +1054,29 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>M-14</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>基本設計書 (01) v1.0 確定</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>第 2 回独立確認 無条件合格 (10 シート 31,860 bytes)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
+    <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>M-15</t>
@@ -1101,23 +1098,23 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>M-16</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>本中間版 提出</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
         <is>
           <t>5 件 xlsx + 公開発布版資料 + 案内 → クラウド集約</t>
         </is>
@@ -1178,7 +1175,7 @@
           <t>本中間版同梱物 案内 (00 納品範囲)</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>../00_納品範囲.xlsx</t>
         </is>
@@ -1190,7 +1187,7 @@
           <t>進捗報告書 (07)</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>../07_進捗報告書.xlsx</t>
         </is>
@@ -1202,9 +1199,9 @@
           <t>要件定義書 (04, 第 1 段階 第 1 着手 確定版)</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>../04_要件定義書.xlsx</t>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>../01_要件定義書.xlsx</t>
         </is>
       </c>
     </row>
@@ -1214,9 +1211,9 @@
           <t>基本設計書 (01, 第 1 段階 第 2 着手 確定版)</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>../01_基本設計書.xlsx</t>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>../02_基本設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1223,7 @@
           <t>公開発布版 README (日本語)</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>../../ai_platforms/release/v1.0/README.ja.md</t>
         </is>
@@ -1238,7 +1235,7 @@
           <t>公開発布版 改訂履歴</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>../../ai_platforms/release/v1.0/CHANGELOG.md</t>
         </is>
@@ -1292,56 +1289,56 @@
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>役割</t>
         </is>
       </c>
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="22" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="C2" s="21" t="inlineStr">
+      <c r="C2" s="22" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="D2" s="21" t="inlineStr">
+      <c r="D2" s="22" t="inlineStr">
         <is>
           <t>押印・署名</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>作成</t>
         </is>
       </c>
-      <c r="B3" s="23" t="n"/>
-      <c r="C3" s="23" t="n"/>
-      <c r="D3" s="23" t="n"/>
+      <c r="B3" s="24" t="n"/>
+      <c r="C3" s="24" t="n"/>
+      <c r="D3" s="24" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
       </c>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
+      <c r="B4" s="26" t="n"/>
+      <c r="C4" s="26" t="n"/>
+      <c r="D4" s="26" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>承認</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n"/>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="23" t="n"/>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1366,15 +1363,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1398,18 +1393,8 @@
           <t>作成</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>承認</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
+    </row>
+    <row r="2" ht="16.5" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
           <t>v0.5</t>
@@ -1428,16 +1413,6 @@
       <c r="D2" s="7" t="inlineStr">
         <is>
           <t>(担当部門)</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>(日本側ネイティブ確認担当指名待ち)</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>Bojiang Zhang</t>
         </is>
       </c>
     </row>
@@ -1742,11 +1717,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="2" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1756,142 +1732,128 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2">
       <c r="B2" s="17" t="inlineStr">
         <is>
           <t>1.1 本書の目的</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="B3" s="17" t="inlineStr">
+    <row r="3">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>本書は, SDTM 知識ベース構築および iTMS 様向け納品ドキュメント整備の全工程における, 検査・修正・反復の実績を集約し提示する補助文書である。受信者向け納品物 (要件定義書 / 基本設計書 等) は最終確定版のみを提示するため, 結果に至る過程の試行錯誤の規模を可視化する目的で作成した。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
+    <row r="4">
       <c r="B4" s="17" t="inlineStr">
         <is>
           <t>1.2 整備期間</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="B5" s="17" t="inlineStr">
+    <row r="5">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>整備期間は 2026 年 4 月 13 日 (本知識ベース構築開始) から 2026 年 4 月 30 日 (本中間版提出日) までの約 18 日間である。期間中の成果物変更件数は 267 件 (重要マイルストーンは §7 に詳述する)。</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
+    <row r="6">
       <c r="B6" s="17" t="inlineStr">
         <is>
           <t>1.3 反復方針</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="17" t="inlineStr">
+    <row r="7">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>本整備では「作成担当 + 独立確認担当 + 用語監査担当」の三役完全分離体制を採用した。同一担当者による自審を禁じ, 異なる種別の確認担当者が独立に検査することで, 単一視点では見落としやすい不整合を多角的に検出する方針である。</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="B8" s="17" t="inlineStr">
+    <row r="8">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>なお本書中の「回次」は同一作業対象に対する独立確認担当の検査循環を指す。第 1 回が条件付合格の場合は指摘事項を反映後に第 2 回に進む方式とした。確認担当は第 1 回と第 2 回で別の担当者を割り当て, 同一文脈での自審を回避している。</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
+    <row r="9">
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>出典: docs/jp/PLAN.md §6 + docs/jp/CHANGELOG.md。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="B10" s="17" t="inlineStr">
-        <is>
           <t>1.4 反復総数概況</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="17" t="inlineStr">
+    <row r="10">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>下表に各工程系統の反復総数概況を示す。詳細は §2 - §6 の各シートを参照されたい。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="B12" s="17" t="inlineStr">
+    <row r="11">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>- AI 平台 4 種プロンプト整備: 4 平台 × 多数版数 = 累計 18 版超 (各平台 4 - 7 版進化)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="B13" s="17" t="inlineStr">
+    <row r="12">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>- smoke 動作試験: v2 → v4.0 → v5c 回帰確認 = 9 反復</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="17" t="inlineStr">
+    <row r="13">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>- 知識ベース字面級確認 (公開発布版): 14 回次 (各回次に複数バッチを含む)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="B15" s="17" t="inlineStr">
+    <row r="14">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>- 受信者向け文書整備 (本中間版): 第 0 - 第 0.7 + 第 1 段階 第 1-2 着手 = 計 16 反復</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="B16" s="17" t="inlineStr">
+    <row r="15">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>- 用語写像辞書 整備: 第 1 - 第 3 回独立確認 = 3 反復で確定</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
+    <row r="16">
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>合計反復回数 (独立確認担当による検査循環) は約 50 回次相当である。検出された不整合は所定の手順で修正後再確認する方式 (合格判定基準充足まで反復) を一貫して適用した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>合計反復回数 (独立確認担当による検査循環) は約 50 回次相当である。検出された不整合は所定の手順で修正後再確認する方式 (合格判定基準充足まで反復) を一貫して適用した。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="17" t="inlineStr">
-        <is>
           <t>1.5 反復の意義</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="B19" s="17" t="inlineStr">
+    <row r="18">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>多重反復は工数増大の側面はあるものの, 単一視点では検出不能な不整合 (主張文と引用源のずれ, 用語の混在, 数値と本文の乖離等) を体系的に解消する効果が確認できた。本中間版に同梱する確定版 2 件 (要件定義書 v1.0 / 基本設計書 v1.0) は, いずれも独立確認担当による検査の第 2 回において無条件合格を取得している。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>出典: docs/jp/glossary/research_reports/phase_1_04_reviewer_round_2_2026-04-29.md + phase_1_01_reviewer_round_2_2026-04-29.md。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -1962,7 +1924,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>A</t>
@@ -1994,39 +1956,39 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>smoke 動作試験</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>2026-04-18 〜 2026-04-24</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>9 反復 (v2 / v2.1 / v3 / v3.1 / v3.2 / v4.0 R1 / v4.0 R2 / v5c 回帰 / 4 平台横断確認)</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>smoke v4.0 (3 + 14 + 3 = 20 評価項目, 4 平台共通基準)</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>Claude 17/17 / ChatGPT 16.5/17 / Gemini 16/17 / NotebookLM 15/17 で確定</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>C</t>
@@ -2058,39 +2020,39 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>受信者向け文書整備 (本中間版)</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>2026-04-29 〜 2026-04-30</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>16 反復</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>要件定義書 v1.0 / 基本設計書 v1.0 / 用語集 v0.1 骨格 / 進捗報告書 v0.5 / 反復実績記録 v0.5 (本書)</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>確定 2 件 + 中間 / 骨格版 3 件 (本日提出)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>E</t>
@@ -2201,7 +2163,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>A-1</t>
@@ -2238,44 +2200,44 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>A-2</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>ChatGPT GPTs</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>N3B → N4 → N5.2 → N5.3 → v2.1 → v2.2 (6 版経由, Q1 GFINHERT 拼写修正)</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>v2.2</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>16.5/17 (97%) PASS</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>9 ファイル + 系統プロンプト. Gemini と整合をとり並列展開</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>A-3</t>
@@ -2312,38 +2274,38 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>A-4</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>NotebookLM</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>v1 (3 ノートブック方式 SUPERSEDED) → v2 (1 ノートブック × 42 文献構成)</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>v2</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>15/17 (88%) 主要部合格</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>アーキテクチャ転換 1 件実施. 第 3.5 / 3.6 / 3.7 段階の精緻化作業を経て確定</t>
         </is>
@@ -2428,7 +2390,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>B-1</t>
@@ -2465,44 +2427,44 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>B-2</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>smoke v2.1</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>2026-04-19 周辺</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>24 項目 (微調整)</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>Gemini (Q3 再試験)</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>Gemini Q3 単独再試験用</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>Gemini v3-v5 系の不具合特定に貢献</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>B-3</t>
@@ -2539,44 +2501,44 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>B-4</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>smoke v3.1</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>2026-04-21 周辺</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>再構成版 + 修正</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>ChatGPT / Gemini</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>問題項目 5 件の修正適用</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>Gemini Q10 SUPP-- 不具合の系統的特定</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>B-5</t>
@@ -2613,44 +2575,44 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>B-6</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>smoke v4.0 R1</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>2026-04-23 周辺</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>20 項目 (3 + 14 + 3)</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>全 4 平台横断</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>3 個の汎化耐性確認項目 (AHP) を新規追加. 4 平台横断 ground truth 化</t>
         </is>
       </c>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>全 4 平台のベースライン取得</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
+    <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>B-7</t>
@@ -2687,44 +2649,44 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>B-8</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>smoke v5c 回帰</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>14 項目 (Q4-Q10 ×2)</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>Gemini + ChatGPT 双方</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>Q4-Q10 全項目の二重平台一括回帰確認 (14/14 厳格合格)</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t>第 15 番目独立確認担当の承認取得</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
+    <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>B-9</t>
@@ -2834,7 +2796,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>C-01</t>
@@ -2866,39 +2828,39 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>C-02</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>第 2 回</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>2026-04-17 周辺</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>P0 段階 標準化版</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>200 項目超</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>検証単位データ schema 確定 (atom_schema v1.2)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>C-03</t>
@@ -2930,39 +2892,39 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>C-04</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>第 4 - 第 7 回</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>2026-04-20 〜 2026-04-23</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>P1 段階 前半 (ig34 中盤)</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>計 4,000 項目超</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>整備手順の検査と再点検実施</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>C-05</t>
@@ -2994,39 +2956,39 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>C-06</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>第 9 - 第 11 回</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>2026-04-26 〜 2026-04-28</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>P1 段階 後半 (ig34 完結)</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>計 3,500 項目超</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>ig34 全 461 頁 100% 完了到達</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
+    <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>C-07</t>
@@ -3058,39 +3020,39 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>C-08</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>第 13 回</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>2026-04-29 周辺</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>P1 段階 (sv20 中盤)</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>440 項目超</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>整備手順の精緻化 (作業工程 v1.7 → v1.8)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
+    <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>C-09</t>
@@ -3122,33 +3084,33 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>C-10</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>P1 → P2 移行</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>2026-04-30 周辺</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>P2 段階 ch04 L601-900 進行中</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>現在 238 項目処理中</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>P2 段階開始. 公開発布版とは別系統で継続中</t>
         </is>
@@ -3227,7 +3189,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>D-01</t>
@@ -3259,39 +3221,39 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>D-02</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>第 0.5 段階</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>用語調研 (16 規格一次資料調査)</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>3 班 + 1 統合</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>IT 規格 7 件 / 医療規格 5 件 / 補助規格 4 件を 3 班並列調査 + 統合担当が一本化</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>D-03</t>
@@ -3323,39 +3285,39 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>D-04</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>第 0.7 段階</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>Excel 基盤構築 (生成処理)</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>スタイル指針 / 表紙統一様式 / 生成処理 754 行 (検査機能 + CJK 列幅自動調整)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>D-05</t>
@@ -3387,39 +3349,39 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>D-06</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>第 0.5.8 段階</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>用語集骨格作成 + 軽微修正</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>1 + 2 修正</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>33 項目 / 7 シート 骨格作成 + 列幅自動調整 + 注意行スタイル区別 修正</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
+    <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>D-07</t>
@@ -3451,39 +3413,39 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>D-08</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>第 1 段階 第 1 着手</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>要件定義書 (04) 独立確認</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>2 回</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>第 1 回条件付合格 (中等 1 + 軽微 4) → 第 2 回無条件合格</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
+    <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>D-09</t>
@@ -3515,39 +3477,39 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>D-10</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>第 1 段階 第 2 着手</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>基本設計書 (01) 作成担当</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>2 回</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>第 1 回起草 (9/9 自己検査合格) → 第 2 回 反映 (10 件指摘)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
+    <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>D-11</t>
@@ -3579,39 +3541,39 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>D-12</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>第 1 段階 第 2 着手</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>基本設計書 (01) 用語監査</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E14" s="19" t="inlineStr">
         <is>
           <t>1 回</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="19" t="inlineStr">
         <is>
           <t>中等 1 件指摘 (トレーサビリティ管理表の正式名称復元) → 主担当補正で確定</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
+    <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>D-13</t>
@@ -3643,39 +3605,39 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>D-14</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>第 1 段階 (本中間版)</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>進捗報告書 (07) 作成 + 監査</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>1 + 1 修正</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>中間版起草 + 用語監査機械検査 1 件指摘 (内部ファイル名引用) → 修正適用後合格</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
+    <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>D-15</t>
@@ -3707,33 +3669,33 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>D-16</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>第 1 段階 (本中間版)</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
         <is>
           <t>中間版集約 + 検査</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="19" t="inlineStr">
         <is>
           <t>1 サイクル</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>全 4 件 xlsx + 公開発布版 + 案内 README + 集約処理 + sha256 算出</t>
         </is>
